--- a/Auswahl_Folientyp.xlsx
+++ b/Auswahl_Folientyp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aquasun-my.sharepoint.com/personal/michael_hiller_aquasun_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="375" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91BEBAC7-EC5E-4D7C-9B65-84CE0CD1D16D}"/>
+  <xr:revisionPtr revIDLastSave="386" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4798A0CE-2637-4B86-8612-0DC5F138197F}"/>
   <bookViews>
-    <workbookView xWindow="9375" yWindow="0" windowWidth="38625" windowHeight="22995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5715" yWindow="195" windowWidth="24150" windowHeight="22515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="118">
   <si>
     <t>Einheit</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>SL 8</t>
+  </si>
+  <si>
+    <t>In dem EK - Preis sind Nebenkosten wie Klingen, Papier und Silikon bereits enthalten.</t>
+  </si>
+  <si>
+    <t>Opak Weiß</t>
   </si>
 </sst>
 </file>
@@ -447,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -471,6 +477,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -808,7 +820,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:Q103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="5" customWidth="1"/>
@@ -928,7 +940,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N4">
         <v>1524</v>
@@ -944,7 +956,7 @@
       <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="10" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -957,7 +969,7 @@
         <v>1524</v>
       </c>
       <c r="P5">
-        <v>30480</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -1777,68 +1789,65 @@
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
+      <c r="B51" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="N51">
+        <v>1524</v>
+      </c>
+      <c r="O51">
+        <v>1829</v>
+      </c>
+      <c r="P51">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D51" s="2">
+      <c r="C52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2">
         <v>4.5</v>
       </c>
-      <c r="L51">
+      <c r="L52">
         <v>1370</v>
       </c>
-      <c r="P51">
+      <c r="P52">
         <v>25000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="2">
-        <v>16</v>
-      </c>
-      <c r="N52">
-        <v>1524</v>
-      </c>
-      <c r="P52">
-        <v>50000</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D53" s="2">
-        <v>46</v>
-      </c>
-      <c r="E53">
-        <v>914</v>
+        <v>16</v>
       </c>
       <c r="N53">
         <v>1524</v>
       </c>
-      <c r="O53">
-        <v>1829</v>
-      </c>
       <c r="P53">
-        <v>30480</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>1</v>
@@ -1849,9 +1858,6 @@
       <c r="E54">
         <v>914</v>
       </c>
-      <c r="H54" s="8">
-        <v>1219</v>
-      </c>
       <c r="N54">
         <v>1524</v>
       </c>
@@ -1863,11 +1869,8 @@
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="B55" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>1</v>
@@ -1878,7 +1881,7 @@
       <c r="E55">
         <v>914</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="8">
         <v>1219</v>
       </c>
       <c r="N55">
@@ -1892,18 +1895,24 @@
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B56" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D56" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E56">
         <v>914</v>
       </c>
+      <c r="H56">
+        <v>1219</v>
+      </c>
       <c r="N56">
         <v>1524</v>
       </c>
@@ -1916,13 +1925,13 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D57" s="2">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E57">
         <v>914</v>
@@ -1939,50 +1948,50 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2">
+        <v>37</v>
+      </c>
+      <c r="E58">
+        <v>914</v>
+      </c>
+      <c r="N58">
+        <v>1524</v>
+      </c>
+      <c r="O58">
+        <v>1829</v>
+      </c>
+      <c r="P58">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B59" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2">
+      <c r="C59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2">
         <v>20</v>
       </c>
-      <c r="N58">
-        <v>1524</v>
-      </c>
-      <c r="P58">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
+      <c r="N59">
+        <v>1524</v>
+      </c>
+      <c r="P59">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="2">
-        <v>14.5</v>
-      </c>
-      <c r="H59">
-        <v>1219</v>
-      </c>
-      <c r="N59">
-        <v>1524</v>
-      </c>
-      <c r="O59">
-        <v>1829</v>
-      </c>
-      <c r="P59">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B60" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>1</v>
@@ -2005,7 +2014,7 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>1</v>
@@ -2028,16 +2037,22 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D62" s="2">
-        <v>5</v>
+        <v>14.5</v>
+      </c>
+      <c r="H62">
+        <v>1219</v>
       </c>
       <c r="N62">
         <v>1524</v>
+      </c>
+      <c r="O62">
+        <v>1829</v>
       </c>
       <c r="P62">
         <v>30480</v>
@@ -2045,22 +2060,16 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D63" s="2">
-        <v>11</v>
-      </c>
-      <c r="H63">
-        <v>1219</v>
+        <v>5</v>
       </c>
       <c r="N63">
         <v>1524</v>
-      </c>
-      <c r="O63">
-        <v>1829</v>
       </c>
       <c r="P63">
         <v>30480</v>
@@ -2068,141 +2077,141 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2">
+        <v>11</v>
+      </c>
+      <c r="H64">
+        <v>1219</v>
+      </c>
+      <c r="N64">
+        <v>1524</v>
+      </c>
+      <c r="O64">
+        <v>1829</v>
+      </c>
+      <c r="P64">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D64" s="2">
+      <c r="C65" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2">
         <v>5</v>
       </c>
-      <c r="N64">
-        <v>1524</v>
-      </c>
-      <c r="P64">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B65" s="1" t="s">
+      <c r="N65">
+        <v>1524</v>
+      </c>
+      <c r="P65">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="2">
+      <c r="C66" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2">
         <v>11</v>
       </c>
-      <c r="H65">
+      <c r="H66">
         <v>1219</v>
       </c>
-      <c r="N65">
-        <v>1524</v>
-      </c>
-      <c r="O65">
+      <c r="N66">
+        <v>1524</v>
+      </c>
+      <c r="O66">
         <v>1829</v>
       </c>
-      <c r="P65">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B66" s="1" t="s">
+      <c r="P66">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D66" s="2">
+      <c r="C67" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
         <v>6</v>
       </c>
-      <c r="N66">
-        <v>1524</v>
-      </c>
-      <c r="P66">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B67" s="1" t="s">
+      <c r="N67">
+        <v>1524</v>
+      </c>
+      <c r="P67">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D67" s="2">
+      <c r="C68" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
         <v>7.5</v>
       </c>
-      <c r="N67">
-        <v>1524</v>
-      </c>
-      <c r="P67">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B68" s="1" t="s">
+      <c r="N68">
+        <v>1524</v>
+      </c>
+      <c r="P68">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="2">
+      <c r="C69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2">
         <v>19</v>
       </c>
-      <c r="H68">
+      <c r="H69">
         <v>1219</v>
       </c>
-      <c r="N68">
-        <v>1524</v>
-      </c>
-      <c r="P68">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B69" s="4" t="s">
+      <c r="N69">
+        <v>1524</v>
+      </c>
+      <c r="P69">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B70" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D69" s="2">
+      <c r="C70" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
         <v>30</v>
       </c>
-      <c r="N69">
-        <v>1524</v>
-      </c>
-      <c r="P69">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B70" s="1" t="s">
+      <c r="N70">
+        <v>1524</v>
+      </c>
+      <c r="P70">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B71" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D70" s="2">
-        <v>21.5</v>
-      </c>
-      <c r="E70">
-        <v>914</v>
-      </c>
-      <c r="N70">
-        <v>1524</v>
-      </c>
-      <c r="O70">
-        <v>1829</v>
-      </c>
-      <c r="P70">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B71" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>1</v>
@@ -2210,48 +2219,48 @@
       <c r="D71" s="2">
         <v>21.5</v>
       </c>
-      <c r="K71">
+      <c r="E71">
+        <v>914</v>
+      </c>
+      <c r="N71">
+        <v>1524</v>
+      </c>
+      <c r="O71">
+        <v>1829</v>
+      </c>
+      <c r="P71">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="K72">
         <v>1270</v>
       </c>
-      <c r="N71">
-        <v>1524</v>
-      </c>
-      <c r="P71">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B72" s="1" t="s">
+      <c r="N72">
+        <v>1524</v>
+      </c>
+      <c r="P72">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="2">
+      <c r="C73" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2">
         <v>19.5</v>
-      </c>
-      <c r="O72">
-        <v>1829</v>
-      </c>
-      <c r="P72">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B73" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="2">
-        <v>12</v>
-      </c>
-      <c r="K73">
-        <v>1270</v>
-      </c>
-      <c r="N73">
-        <v>1524</v>
       </c>
       <c r="O73">
         <v>1829</v>
@@ -2260,15 +2269,18 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D74" s="2">
-        <v>26.5</v>
+        <v>12</v>
+      </c>
+      <c r="K74">
+        <v>1270</v>
       </c>
       <c r="N74">
         <v>1524</v>
@@ -2280,18 +2292,15 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D75" s="2">
-        <v>12.5</v>
-      </c>
-      <c r="H75">
-        <v>1219</v>
+        <v>26.5</v>
       </c>
       <c r="N75">
         <v>1524</v>
@@ -2303,15 +2312,15 @@
         <v>30480</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D76" s="2">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="H76">
         <v>1219</v>
@@ -2319,67 +2328,70 @@
       <c r="N76">
         <v>1524</v>
       </c>
+      <c r="O76">
+        <v>1829</v>
+      </c>
       <c r="P76">
         <v>30480</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2">
+        <v>6</v>
+      </c>
+      <c r="H77">
+        <v>1219</v>
+      </c>
+      <c r="N77">
+        <v>1524</v>
+      </c>
+      <c r="P77">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D77" s="2">
+      <c r="C78" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2">
         <v>16.5</v>
       </c>
-      <c r="N77">
-        <v>1524</v>
-      </c>
-      <c r="P77">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B78" s="1" t="s">
+      <c r="N78">
+        <v>1524</v>
+      </c>
+      <c r="P78">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C78" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" s="2">
+      <c r="C79" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2">
         <v>28.5</v>
       </c>
-      <c r="G78">
+      <c r="G79">
         <v>1080</v>
       </c>
-      <c r="P78">
+      <c r="P79">
         <v>50000</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B79" s="1" t="s">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D79" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="N79">
-        <v>1524</v>
-      </c>
-      <c r="P79">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A80" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>1</v>
@@ -2395,23 +2407,20 @@
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B81" s="1" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D81" s="2">
-        <v>11</v>
-      </c>
-      <c r="H81">
-        <v>1219</v>
+        <v>2.5</v>
       </c>
       <c r="N81">
         <v>1524</v>
-      </c>
-      <c r="O81">
-        <v>1829</v>
       </c>
       <c r="P81">
         <v>30480</v>
@@ -2419,90 +2428,93 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2">
+        <v>11</v>
+      </c>
+      <c r="H82">
+        <v>1219</v>
+      </c>
+      <c r="N82">
+        <v>1524</v>
+      </c>
+      <c r="O82">
+        <v>1829</v>
+      </c>
+      <c r="P82">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B83" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" s="2">
+      <c r="C83" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2">
         <v>6.5</v>
       </c>
-      <c r="N82">
-        <v>1524</v>
-      </c>
-      <c r="P82">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" s="5" t="s">
+      <c r="N83">
+        <v>1524</v>
+      </c>
+      <c r="P83">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B84" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D83" s="2">
+      <c r="C84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2">
         <v>9.5</v>
       </c>
-      <c r="N83">
-        <v>1524</v>
-      </c>
-      <c r="P83">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B84" s="1" t="s">
+      <c r="N84">
+        <v>1524</v>
+      </c>
+      <c r="P84">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B85" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D84" s="2">
+      <c r="C85" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2">
         <v>4</v>
       </c>
-      <c r="N84">
-        <v>1524</v>
-      </c>
-      <c r="P84">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A85" s="5" t="s">
+      <c r="N85">
+        <v>1524</v>
+      </c>
+      <c r="P85">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D85" s="2">
+      <c r="C86" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D86" s="2">
         <v>8.5</v>
-      </c>
-      <c r="N85">
-        <v>1524</v>
-      </c>
-      <c r="P85">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B86" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D86" s="2">
-        <v>14</v>
-      </c>
-      <c r="H86">
-        <v>1219</v>
       </c>
       <c r="N86">
         <v>1524</v>
@@ -2513,7 +2525,7 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>1</v>
@@ -2532,40 +2544,40 @@
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A88" s="5" t="s">
+      <c r="B88" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88" s="2">
+        <v>14</v>
+      </c>
+      <c r="H88">
+        <v>1219</v>
+      </c>
+      <c r="N88">
+        <v>1524</v>
+      </c>
+      <c r="P88">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D88" s="2">
+      <c r="C89" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="2">
         <v>11</v>
       </c>
-      <c r="N88">
-        <v>1524</v>
-      </c>
-      <c r="P88">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B89" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89" s="2">
-        <v>10.5</v>
-      </c>
       <c r="N89">
         <v>1524</v>
-      </c>
-      <c r="O89">
-        <v>1829</v>
       </c>
       <c r="P89">
         <v>30480</v>
@@ -2573,16 +2585,19 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D90" s="2">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="N90">
         <v>1524</v>
+      </c>
+      <c r="O90">
+        <v>1829</v>
       </c>
       <c r="P90">
         <v>30480</v>
@@ -2590,19 +2605,16 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D91" s="2">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="N91">
         <v>1524</v>
-      </c>
-      <c r="O91">
-        <v>1829</v>
       </c>
       <c r="P91">
         <v>30480</v>
@@ -2610,50 +2622,53 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="N92">
+        <v>1524</v>
+      </c>
+      <c r="O92">
+        <v>1829</v>
+      </c>
+      <c r="P92">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B93" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D92" s="2">
+      <c r="C93" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2">
         <v>9</v>
       </c>
-      <c r="N92">
-        <v>1524</v>
-      </c>
-      <c r="P92">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A93" s="5" t="s">
+      <c r="N93">
+        <v>1524</v>
+      </c>
+      <c r="P93">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D93" s="2">
+      <c r="C94" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2">
         <v>4</v>
-      </c>
-      <c r="N93">
-        <v>1524</v>
-      </c>
-      <c r="P93">
-        <v>30480</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B94" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D94" s="2">
-        <v>8.5</v>
       </c>
       <c r="N94">
         <v>1524</v>
@@ -2664,30 +2679,30 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D95" s="2">
-        <v>15.5</v>
-      </c>
-      <c r="I95">
-        <v>1250</v>
+        <v>8.5</v>
+      </c>
+      <c r="N95">
+        <v>1524</v>
       </c>
       <c r="P95">
-        <v>25000</v>
+        <v>30480</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D96" s="2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="I96">
         <v>1250</v>
@@ -2698,27 +2713,24 @@
     </row>
     <row r="97" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D97" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="F97">
-        <v>1000</v>
-      </c>
-      <c r="J97">
-        <v>1260</v>
+        <v>16.5</v>
+      </c>
+      <c r="I97">
+        <v>1250</v>
       </c>
       <c r="P97">
-        <v>50000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="98" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>1</v>
@@ -2738,41 +2750,66 @@
     </row>
     <row r="99" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D99" s="2">
-        <v>10</v>
-      </c>
-      <c r="N99">
-        <v>1524</v>
+        <v>10.5</v>
+      </c>
+      <c r="F99">
+        <v>1000</v>
+      </c>
+      <c r="J99">
+        <v>1260</v>
       </c>
       <c r="P99">
-        <v>30480</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="100" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2">
+        <v>10</v>
+      </c>
+      <c r="N100">
+        <v>1524</v>
+      </c>
+      <c r="P100">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B101" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D100" s="2">
+      <c r="C101" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2">
         <v>19.5</v>
       </c>
-      <c r="N100">
-        <v>1524</v>
-      </c>
-      <c r="P100">
-        <v>30480</v>
+      <c r="N101">
+        <v>1524</v>
+      </c>
+      <c r="P101">
+        <v>30480</v>
+      </c>
+    </row>
+    <row r="103" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B103" s="9" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:P100">
-    <sortCondition ref="B4:B100"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:P101">
+    <sortCondition ref="B4:B101"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup scale="70" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/Auswahl_Folientyp.xlsx
+++ b/Auswahl_Folientyp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aquasun-my.sharepoint.com/personal/michael_hiller_aquasun_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="386" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4798A0CE-2637-4B86-8612-0DC5F138197F}"/>
+  <xr:revisionPtr revIDLastSave="568" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{299F3C04-5A38-453D-A8AD-B8793ECFC919}"/>
   <bookViews>
-    <workbookView xWindow="5715" yWindow="195" windowWidth="24150" windowHeight="22515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14010" yWindow="2775" windowWidth="27720" windowHeight="22170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="122">
   <si>
     <t>Einheit</t>
   </si>
@@ -341,9 +341,6 @@
     <t>Data Blokker</t>
   </si>
   <si>
-    <t>Preis prüfen</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
@@ -387,6 +384,21 @@
   </si>
   <si>
     <t>Opak Weiß</t>
+  </si>
+  <si>
+    <t>Preis</t>
+  </si>
+  <si>
+    <t>aktuell</t>
+  </si>
+  <si>
+    <t>aktuell EOL</t>
+  </si>
+  <si>
+    <t>Alt - Menge mit Bestand prüfen</t>
+  </si>
+  <si>
+    <t>aktuell EOL - Menge mit Bestand prüfen</t>
   </si>
 </sst>
 </file>
@@ -422,7 +434,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -476,13 +487,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -836,7 +847,7 @@
     <col min="12" max="13" width="5" customWidth="1"/>
     <col min="14" max="15" width="6" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="36.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -890,49 +901,46 @@
         <v>39</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="L3" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="P3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" t="s">
-        <v>102</v>
+      <c r="Q3" s="6" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="B4" s="1" t="s">
         <v>98</v>
       </c>
@@ -940,7 +948,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>1524</v>
@@ -951,12 +959,12 @@
       <c r="P4">
         <v>30480</v>
       </c>
+      <c r="Q4" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -970,6 +978,9 @@
       </c>
       <c r="P5">
         <v>20000</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -991,6 +1002,9 @@
       <c r="P6">
         <v>30480</v>
       </c>
+      <c r="Q6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
@@ -1008,6 +1022,9 @@
       <c r="P7">
         <v>30480</v>
       </c>
+      <c r="Q7" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
@@ -1025,8 +1042,14 @@
       <c r="P8">
         <v>30480</v>
       </c>
+      <c r="Q8" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B9" s="1" t="s">
         <v>44</v>
       </c>
@@ -1041,6 +1064,9 @@
       </c>
       <c r="P9">
         <v>30480</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -1059,8 +1085,14 @@
       <c r="P10">
         <v>30480</v>
       </c>
+      <c r="Q10" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1076,11 +1108,11 @@
       <c r="P11">
         <v>50000</v>
       </c>
+      <c r="Q11" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="B12" s="1" t="s">
         <v>96</v>
       </c>
@@ -1098,6 +1130,9 @@
       </c>
       <c r="P12">
         <v>30480</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,8 +1154,14 @@
       <c r="P13">
         <v>30480</v>
       </c>
+      <c r="Q13" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B14" s="1" t="s">
         <v>58</v>
       </c>
@@ -1135,6 +1176,9 @@
       </c>
       <c r="P14">
         <v>30480</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1153,6 +1197,9 @@
       <c r="P15">
         <v>30480</v>
       </c>
+      <c r="Q15" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
@@ -1170,8 +1217,14 @@
       <c r="P16">
         <v>30480</v>
       </c>
+      <c r="Q16" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
@@ -1186,6 +1239,9 @@
       </c>
       <c r="P17">
         <v>30480</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -1207,6 +1263,9 @@
       <c r="P18">
         <v>30480</v>
       </c>
+      <c r="Q18" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
@@ -1216,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="7">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="H19">
         <v>1219</v>
@@ -1229,6 +1288,9 @@
       </c>
       <c r="P19">
         <v>30480</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1250,8 +1312,14 @@
       <c r="P20">
         <v>30480</v>
       </c>
+      <c r="Q20" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B21" s="1" t="s">
         <v>62</v>
       </c>
@@ -1266,6 +1334,9 @@
       </c>
       <c r="P21">
         <v>30480</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1284,11 +1355,11 @@
       <c r="P22">
         <v>30480</v>
       </c>
+      <c r="Q22" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
@@ -1304,11 +1375,11 @@
       <c r="P23">
         <v>30480</v>
       </c>
+      <c r="Q23" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="B24" s="1" t="s">
         <v>8</v>
       </c>
@@ -1323,6 +1394,9 @@
       </c>
       <c r="P24">
         <v>30480</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -1341,6 +1415,9 @@
       <c r="P25">
         <v>30480</v>
       </c>
+      <c r="Q25" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
@@ -1358,6 +1435,9 @@
       <c r="P26">
         <v>30480</v>
       </c>
+      <c r="Q26" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
@@ -1375,6 +1455,9 @@
       <c r="P27">
         <v>30480</v>
       </c>
+      <c r="Q27" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
@@ -1392,11 +1475,11 @@
       <c r="P28">
         <v>30480</v>
       </c>
+      <c r="Q28" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="B29" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,6 +1494,9 @@
       </c>
       <c r="P29">
         <v>30480</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -1429,11 +1515,14 @@
       <c r="P30">
         <v>30480</v>
       </c>
-      <c r="Q30">
-        <v>6.5</v>
+      <c r="Q30" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B31" s="1" t="s">
         <v>15</v>
       </c>
@@ -1448,6 +1537,9 @@
       </c>
       <c r="P31">
         <v>30480</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -1466,11 +1558,11 @@
       <c r="P32">
         <v>30480</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="Q32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>17</v>
       </c>
@@ -1486,8 +1578,11 @@
       <c r="P33">
         <v>30480</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>18</v>
       </c>
@@ -1503,8 +1598,11 @@
       <c r="P34">
         <v>30480</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>19</v>
       </c>
@@ -1520,8 +1618,11 @@
       <c r="P35">
         <v>30480</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>20</v>
       </c>
@@ -1537,8 +1638,11 @@
       <c r="P36">
         <v>50000</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>21</v>
       </c>
@@ -1554,8 +1658,11 @@
       <c r="P37">
         <v>50000</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q37" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>22</v>
       </c>
@@ -1563,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="2">
-        <v>30.5</v>
+        <v>33.5</v>
       </c>
       <c r="N38">
         <v>1524</v>
@@ -1574,8 +1681,14 @@
       <c r="P38">
         <v>30480</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q38" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B39" s="1" t="s">
         <v>23</v>
       </c>
@@ -1591,8 +1704,11 @@
       <c r="P39">
         <v>30480</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1727,11 @@
       <c r="P40">
         <v>30480</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q40" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>25</v>
       </c>
@@ -1628,8 +1747,11 @@
       <c r="P41">
         <v>30480</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>26</v>
       </c>
@@ -1645,8 +1767,11 @@
       <c r="P42">
         <v>30480</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q42" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
@@ -1665,8 +1790,11 @@
       <c r="P43">
         <v>30480</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q43" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>28</v>
       </c>
@@ -1674,7 +1802,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="2">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F44">
         <v>1000</v>
@@ -1685,8 +1813,11 @@
       <c r="P44">
         <v>50000</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>63</v>
       </c>
@@ -1702,8 +1833,11 @@
       <c r="P45">
         <v>30480</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q45" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>64</v>
       </c>
@@ -1711,7 +1845,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="N46">
         <v>1524</v>
@@ -1719,8 +1853,14 @@
       <c r="P46">
         <v>30480</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q46" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B47" s="1" t="s">
         <v>65</v>
       </c>
@@ -1736,8 +1876,11 @@
       <c r="P47">
         <v>30480</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
         <v>66</v>
       </c>
@@ -1753,8 +1896,11 @@
       <c r="P48">
         <v>30480</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q48" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>94</v>
       </c>
@@ -1770,8 +1916,11 @@
       <c r="P49">
         <v>30480</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q49" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>29</v>
       </c>
@@ -1787,10 +1936,13 @@
       <c r="P50">
         <v>30480</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q50" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>1</v>
@@ -1807,11 +1959,11 @@
       <c r="P51">
         <v>30480</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="Q51" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>30</v>
       </c>
@@ -1827,8 +1979,11 @@
       <c r="P52">
         <v>25000</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q52" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>31</v>
       </c>
@@ -1844,8 +1999,11 @@
       <c r="P53">
         <v>50000</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q53" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>45</v>
       </c>
@@ -1853,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E54">
         <v>914</v>
@@ -1867,8 +2025,11 @@
       <c r="P54">
         <v>30480</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q54" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>46</v>
       </c>
@@ -1876,12 +2037,12 @@
         <v>1</v>
       </c>
       <c r="D55" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E55">
         <v>914</v>
       </c>
-      <c r="H55" s="8">
+      <c r="H55" s="10">
         <v>1219</v>
       </c>
       <c r="N55">
@@ -1893,11 +2054,11 @@
       <c r="P55">
         <v>30480</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="Q55" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>47</v>
       </c>
@@ -1905,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E56">
         <v>914</v>
@@ -1922,8 +2083,11 @@
       <c r="P56">
         <v>30480</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q56" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>48</v>
       </c>
@@ -1945,8 +2109,11 @@
       <c r="P57">
         <v>30480</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q57" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>49</v>
       </c>
@@ -1968,8 +2135,11 @@
       <c r="P58">
         <v>30480</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q58" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>50</v>
       </c>
@@ -1985,11 +2155,11 @@
       <c r="P59">
         <v>30480</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="Q59" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>67</v>
       </c>
@@ -2011,8 +2181,11 @@
       <c r="P60">
         <v>30480</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q60" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>68</v>
       </c>
@@ -2034,8 +2207,11 @@
       <c r="P61">
         <v>30480</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q61" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>69</v>
       </c>
@@ -2057,8 +2233,11 @@
       <c r="P62">
         <v>30480</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q62" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>71</v>
       </c>
@@ -2066,7 +2245,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N63">
         <v>1524</v>
@@ -2074,8 +2253,11 @@
       <c r="P63">
         <v>30480</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q63" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>70</v>
       </c>
@@ -2097,8 +2279,11 @@
       <c r="P64">
         <v>30480</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q64" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>73</v>
       </c>
@@ -2106,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="D65" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N65">
         <v>1524</v>
@@ -2114,8 +2299,11 @@
       <c r="P65">
         <v>30480</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q65" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
         <v>72</v>
       </c>
@@ -2137,8 +2325,11 @@
       <c r="P66">
         <v>30480</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q66" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
         <v>75</v>
       </c>
@@ -2154,8 +2345,11 @@
       <c r="P67">
         <v>30480</v>
       </c>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q67" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
         <v>74</v>
       </c>
@@ -2163,16 +2357,22 @@
         <v>1</v>
       </c>
       <c r="D68" s="2">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="N68">
         <v>1524</v>
       </c>
+      <c r="O68">
+        <v>1829</v>
+      </c>
       <c r="P68">
         <v>30480</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q68" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
         <v>76</v>
       </c>
@@ -2180,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="2">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="H69">
         <v>1219</v>
@@ -2191,8 +2391,11 @@
       <c r="P69">
         <v>30480</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q69" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B70" s="4" t="s">
         <v>51</v>
       </c>
@@ -2208,8 +2411,11 @@
       <c r="P70">
         <v>30480</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q70" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
         <v>52</v>
       </c>
@@ -2231,8 +2437,11 @@
       <c r="P71">
         <v>30480</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q71" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
         <v>53</v>
       </c>
@@ -2251,8 +2460,11 @@
       <c r="P72">
         <v>30480</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q72" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
         <v>54</v>
       </c>
@@ -2268,8 +2480,11 @@
       <c r="P73">
         <v>30480</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q73" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
         <v>55</v>
       </c>
@@ -2291,8 +2506,11 @@
       <c r="P74">
         <v>30480</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q74" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
         <v>77</v>
       </c>
@@ -2311,8 +2529,11 @@
       <c r="P75">
         <v>30480</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q75" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
         <v>78</v>
       </c>
@@ -2334,8 +2555,11 @@
       <c r="P76">
         <v>30480</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q76" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
         <v>79</v>
       </c>
@@ -2343,7 +2567,7 @@
         <v>1</v>
       </c>
       <c r="D77" s="2">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H77">
         <v>1219</v>
@@ -2354,8 +2578,11 @@
       <c r="P77">
         <v>30480</v>
       </c>
-    </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q77" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
         <v>80</v>
       </c>
@@ -2363,7 +2590,7 @@
         <v>1</v>
       </c>
       <c r="D78" s="2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="N78">
         <v>1524</v>
@@ -2371,8 +2598,11 @@
       <c r="P78">
         <v>30480</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q78" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>81</v>
       </c>
@@ -2380,7 +2610,7 @@
         <v>1</v>
       </c>
       <c r="D79" s="2">
-        <v>28.5</v>
+        <v>29</v>
       </c>
       <c r="G79">
         <v>1080</v>
@@ -2388,8 +2618,14 @@
       <c r="P79">
         <v>50000</v>
       </c>
-    </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q79" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B80" s="1" t="s">
         <v>32</v>
       </c>
@@ -2405,8 +2641,11 @@
       <c r="P80">
         <v>30480</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q80" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>41</v>
       </c>
@@ -2425,10 +2664,13 @@
       <c r="P81">
         <v>30480</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q81" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>1</v>
@@ -2448,8 +2690,11 @@
       <c r="P82">
         <v>30480</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q82" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
         <v>82</v>
       </c>
@@ -2465,8 +2710,11 @@
       <c r="P83">
         <v>30480</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q83" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>41</v>
       </c>
@@ -2485,10 +2733,16 @@
       <c r="P84">
         <v>30480</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q84" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="B85" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>1</v>
@@ -2502,11 +2756,11 @@
       <c r="P85">
         <v>30480</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A86" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="Q85" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
         <v>84</v>
       </c>
@@ -2514,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="D86" s="2">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N86">
         <v>1524</v>
@@ -2522,8 +2776,11 @@
       <c r="P86">
         <v>30480</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q86" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
         <v>85</v>
       </c>
@@ -2542,8 +2799,11 @@
       <c r="P87">
         <v>30480</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q87" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
         <v>86</v>
       </c>
@@ -2562,8 +2822,11 @@
       <c r="P88">
         <v>30480</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q88" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>41</v>
       </c>
@@ -2582,8 +2845,11 @@
       <c r="P89">
         <v>30480</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q89" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
         <v>100</v>
       </c>
@@ -2591,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="2">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="N90">
         <v>1524</v>
@@ -2602,8 +2868,11 @@
       <c r="P90">
         <v>30480</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q90" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
         <v>88</v>
       </c>
@@ -2619,8 +2888,11 @@
       <c r="P91">
         <v>30480</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q91" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
         <v>89</v>
       </c>
@@ -2628,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="D92" s="2">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="N92">
         <v>1524</v>
@@ -2639,8 +2911,11 @@
       <c r="P92">
         <v>30480</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q92" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
         <v>90</v>
       </c>
@@ -2656,8 +2931,11 @@
       <c r="P93">
         <v>30480</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q93" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
         <v>41</v>
       </c>
@@ -2676,8 +2954,11 @@
       <c r="P94">
         <v>30480</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q94" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
         <v>91</v>
       </c>
@@ -2685,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="D95" s="2">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="N95">
         <v>1524</v>
@@ -2693,8 +2974,11 @@
       <c r="P95">
         <v>30480</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q95" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
         <v>34</v>
       </c>
@@ -2702,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="D96" s="2">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="I96">
         <v>1250</v>
@@ -2710,8 +2994,11 @@
       <c r="P96">
         <v>25000</v>
       </c>
-    </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q96" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
         <v>35</v>
       </c>
@@ -2719,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="D97" s="2">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="I97">
         <v>1250</v>
@@ -2727,8 +3014,11 @@
       <c r="P97">
         <v>25000</v>
       </c>
-    </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q97" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
         <v>36</v>
       </c>
@@ -2747,8 +3037,11 @@
       <c r="P98">
         <v>50000</v>
       </c>
-    </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q98" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
         <v>37</v>
       </c>
@@ -2767,8 +3060,11 @@
       <c r="P99">
         <v>50000</v>
       </c>
-    </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q99" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
         <v>38</v>
       </c>
@@ -2776,7 +3072,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N100">
         <v>1524</v>
@@ -2784,8 +3080,11 @@
       <c r="P100">
         <v>30480</v>
       </c>
-    </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="Q100" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
         <v>93</v>
       </c>
@@ -2801,10 +3100,13 @@
       <c r="P101">
         <v>30480</v>
       </c>
-    </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B103" s="9" t="s">
-        <v>116</v>
+      <c r="Q101" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B103" s="8" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Auswahl_Folientyp.xlsx
+++ b/Auswahl_Folientyp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aquasun-my.sharepoint.com/personal/michael_hiller_aquasun_de/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="568" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{299F3C04-5A38-453D-A8AD-B8793ECFC919}"/>
+  <xr:revisionPtr revIDLastSave="601" documentId="8_{B33A633F-391A-4782-9980-57879B1A347E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2948AEF9-1DFD-4BF2-9CE3-F89FC3B79F05}"/>
   <bookViews>
-    <workbookView xWindow="14010" yWindow="2775" windowWidth="27720" windowHeight="22170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17580" yWindow="1350" windowWidth="27720" windowHeight="22170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -464,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -484,9 +484,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -494,6 +491,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -964,7 +967,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>99</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1142,8 +1145,8 @@
       <c r="C13" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="2">
-        <v>5</v>
+      <c r="D13" s="10">
+        <v>5.5</v>
       </c>
       <c r="H13">
         <v>1219</v>
@@ -1274,7 +1277,7 @@
       <c r="C19" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="11">
         <v>6.5</v>
       </c>
       <c r="H19">
@@ -1396,7 +1399,7 @@
         <v>30480</v>
       </c>
       <c r="Q24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -1416,7 +1419,7 @@
         <v>30480</v>
       </c>
       <c r="Q25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -1456,7 +1459,7 @@
         <v>30480</v>
       </c>
       <c r="Q27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -1559,7 +1562,7 @@
         <v>30480</v>
       </c>
       <c r="Q32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -1589,7 +1592,7 @@
       <c r="C34" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="11">
         <v>4</v>
       </c>
       <c r="N34">
@@ -1599,7 +1602,7 @@
         <v>30480</v>
       </c>
       <c r="Q34" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -1609,7 +1612,7 @@
       <c r="C35" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="11">
         <v>4</v>
       </c>
       <c r="N35">
@@ -1619,7 +1622,7 @@
         <v>30480</v>
       </c>
       <c r="Q35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -1738,8 +1741,8 @@
       <c r="C41" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D41" s="2">
-        <v>4</v>
+      <c r="D41" s="11">
+        <v>5</v>
       </c>
       <c r="N41">
         <v>1524</v>
@@ -1758,8 +1761,8 @@
       <c r="C42" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D42" s="2">
-        <v>4</v>
+      <c r="D42" s="11">
+        <v>5</v>
       </c>
       <c r="N42">
         <v>1524</v>
@@ -2042,7 +2045,7 @@
       <c r="E55">
         <v>914</v>
       </c>
-      <c r="H55" s="10">
+      <c r="H55" s="9">
         <v>1219</v>
       </c>
       <c r="N55">
@@ -2448,8 +2451,8 @@
       <c r="C72" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D72" s="2">
-        <v>21.5</v>
+      <c r="D72" s="10">
+        <v>8</v>
       </c>
       <c r="K72">
         <v>1270</v>
@@ -2491,8 +2494,8 @@
       <c r="C74" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D74" s="2">
-        <v>12</v>
+      <c r="D74" s="10">
+        <v>9.5</v>
       </c>
       <c r="K74">
         <v>1270</v>
@@ -3105,7 +3108,7 @@
       </c>
     </row>
     <row r="103" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="7" t="s">
         <v>115</v>
       </c>
     </row>
